--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>11460.7</v>
+        <v>11509.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>37.32</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.09848484848484848</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>307.0927116827439</v>
+        <v>307.0784418356457</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.04880483345365261</v>
+        <v>0.04867411702367308</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02679528403001072</v>
+        <v>0.02668089647812167</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>91.66666666666666</v>
+        <v>90.15151515151516</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>39.52193338146104</v>
+        <v>39.46964680946923</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>76.02324668110496</v>
+        <v>74.94695464890137</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>38.38009681441979</v>
+        <v>38.37916970247701</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11786.24800538641</v>
+        <v>11785.41563118246</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.02840559524168795</v>
+        <v>0.02399065374805276</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>42.22203310281547</v>
+        <v>42.21897433835395</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12966.07863830218</v>
+        <v>12964.53685572084</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1313513693144552</v>
+        <v>0.1264400837340969</v>
       </c>
     </row>
     <row r="15"/>
@@ -4201,7 +4201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4292,6 +4292,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>11509.3</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0486741170237</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>11509.3</v>
+        <v>11487.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>37.48</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>307.0784418356457</v>
+        <v>307.0622828120824</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.04867411702367308</v>
+        <v>0.04876253047402446</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02668089647812167</v>
+        <v>0.02673082063619353</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>90.15151515151516</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>39.46964680946923</v>
+        <v>39.50501218960979</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>74.94695464890137</v>
+        <v>76.0181703235496</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>38.37916970247701</v>
+        <v>38.38004967681391</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11785.41563118246</v>
+        <v>11785.0656682036</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.02399065374805276</v>
+        <v>0.02593022391911037</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>42.21897433835395</v>
+        <v>42.22104321309217</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12964.53685572084</v>
+        <v>12964.48991171966</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1264400837340969</v>
+        <v>0.1286031332021433</v>
       </c>
     </row>
     <row r="15"/>
@@ -4201,7 +4201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4325,6 +4325,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>11487.2</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.08333333333329999</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.048762530474</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>11487.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>37.41</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>307.0622828120824</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.04876253047402446</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>91.66666666666666</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>39.50501218960979</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>76.0181703235496</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>38.38004967681391</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>11785.0656682036</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.02593022391911037</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>42.22104321309217</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>12964.48991171966</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.1286031332021433</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +811,19 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.2082833385899807</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1232741031990943</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.1148710875237439</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.1192157675747687</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,17 +836,17 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.07458686346488497</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1528696562892018</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1259240259405331</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,17 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.0007631659542847724</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1206514405748893</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1719162001722395</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,17 +882,17 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.08662685146493276</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.07954667332385323</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1148341626541892</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -890,21 +905,20 @@
       <c r="B22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.06389467821337447</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1933551716890769</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.121745661908498</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1040,16 +1054,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>5836.95</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>151.53</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1059,16 +1073,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>6202.85</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>101.87</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1078,16 +1092,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>6330.2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>82.52</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1097,16 +1111,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>6372.35</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>76.45999999999999</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1116,16 +1130,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>6905.8</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>59.95</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1135,16 +1149,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>7195.15</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>62.52</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1154,16 +1168,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>7042.85</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>60.1</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1173,16 +1187,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>7006.4</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>47.85</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1192,16 +1206,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>7051.55</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>47.98</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1211,16 +1225,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>6929.2</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>47.84</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1230,16 +1244,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>6780.6</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>38.11</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1249,16 +1263,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>6829.35</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>38.42</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1268,16 +1282,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>7088.9</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>39.88</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1287,16 +1301,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>6918.5</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>37.1</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1306,16 +1320,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>6692.8</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>35.65</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1325,16 +1339,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>7514.85</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>39.2</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1344,16 +1358,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>7952.75</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>38.21</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1363,16 +1377,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>7872.7</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>39.4</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1382,16 +1396,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>7965.05</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>39.16</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1401,16 +1415,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>7916.5</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>41.1</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1420,16 +1434,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>7554.35</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>39.27</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1439,16 +1453,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>7349.5</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>37.66</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1458,16 +1472,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>7116.35</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>37.43</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1477,16 +1491,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>7161.5</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>37.16</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1496,16 +1510,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>7502.05</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>38.79</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1515,16 +1529,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>7969.75</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>40.4</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1534,16 +1548,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>8318.75</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>42.25</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1553,16 +1567,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>8402.200000000001</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>42.04</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1572,16 +1586,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>8298.450000000001</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>40.19</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1591,16 +1605,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>8459.9</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>40.94</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1610,16 +1624,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>8331.799999999999</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>39.33</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1629,16 +1643,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>8987.1</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>42.53</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1648,16 +1662,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>9577.950000000001</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>45.21</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1667,16 +1681,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>9627.950000000001</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>44.92</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1686,16 +1700,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>9806.15</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>44.86</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1705,16 +1719,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>10128.4</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>47.06</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1724,16 +1738,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>10405.35</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>47.74</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1743,16 +1757,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>10470.9</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>48.12</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1762,16 +1776,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>11131.6</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>50.49</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1781,16 +1795,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>11806.05</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>53.78</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1800,16 +1814,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>12077.7</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>52.87</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1819,16 +1833,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>12826.85</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>52.38</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1838,16 +1852,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>11480.8</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>47.06</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1857,16 +1871,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>11447.4</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>46.63</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1876,16 +1890,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>11362.6</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>46.77</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1895,16 +1909,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>11115.6</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>45.5</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1914,16 +1928,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>10160.7</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>38.63</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1933,16 +1947,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>10720.4</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>40.8</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1952,16 +1966,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>11316.55</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>43.01</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1971,16 +1985,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>11383.15</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>40.64</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1990,16 +2004,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>11842.85</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>41.51</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2009,16 +2023,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>11739.1</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>41.24</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2028,16 +2042,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>12059.35</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>41.18</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2047,16 +2061,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>12063.25</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>41.01</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2066,16 +2080,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>12415.55</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>42.04</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2085,16 +2099,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>12472.15</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>41.07</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2104,16 +2118,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>12289.45</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>40.78</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2123,16 +2137,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>11469</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>38.38</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2142,16 +2156,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>11537.1</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>38.57</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2161,16 +2175,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>10334.35</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>34.47</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2180,16 +2194,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>11417.3</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>37.95</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2199,16 +2213,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>11261</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>36.23</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2218,16 +2232,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>11514.9</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>38.39</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2237,16 +2251,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>12081.85</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>40.3</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2256,16 +2270,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>11802.7</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>38.43</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2367,13 +2381,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>3606.2</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>30.59</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2381,12 +2395,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2394,31 +2408,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>3406.45</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>28.85</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2426,12 +2440,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2439,31 +2453,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>3733.55</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.6</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2471,12 +2485,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2484,31 +2498,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>3879.2</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>32.81</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2516,12 +2530,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2529,28 +2543,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>3517.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>28.67</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2558,15 +2572,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2574,28 +2588,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>3997.9</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>32.43</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2603,15 +2617,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2619,28 +2633,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>4347.3</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>50.43</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2648,15 +2662,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2664,28 +2678,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>4390.65</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>50.7</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2693,15 +2707,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2709,28 +2723,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>5104.4</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>60.43</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2738,15 +2752,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2754,28 +2768,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>4739.75</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>56.42</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2783,15 +2797,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2799,28 +2813,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>5031.45</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>48.67</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2828,15 +2842,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2844,28 +2858,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>4793.2</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>41.94</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2873,15 +2887,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2889,28 +2903,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>4988.85</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>46.79</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2918,15 +2932,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2934,28 +2948,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>4855.4</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>43.99</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2963,15 +2977,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2979,28 +2993,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>4755.5</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>42.92</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3008,15 +3022,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3024,28 +3038,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>4956.15</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>37.44</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3053,15 +3067,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3069,28 +3083,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>4956.6</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>54.78</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3098,15 +3112,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3114,28 +3128,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>4076</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>44.48</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3143,15 +3157,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3159,28 +3173,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>4793.5</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>67.58</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3188,15 +3202,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3204,42 +3218,42 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>5005.05</v>
       </c>
-      <c r="C21" s="7" t="n"/>
+      <c r="C21" s="25" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3247,28 +3261,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>5912.7</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>192.73</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3276,15 +3290,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3292,28 +3306,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>5959.8</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>154.6</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3321,15 +3335,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3337,28 +3351,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>6330.2</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>82.52</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3366,15 +3380,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3382,28 +3396,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>7195.15</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>62.52</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3411,15 +3425,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3427,25 +3441,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>7051.55</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>47.98</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3453,15 +3467,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3469,25 +3483,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>6829.35</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>38.42</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3495,15 +3509,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3511,25 +3525,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>6692.8</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>35.65</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3537,15 +3551,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3553,25 +3567,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>7872.7</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>39.4</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3579,15 +3593,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3595,25 +3609,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>7554.35</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>39.27</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3621,15 +3635,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3637,25 +3651,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>7161.5</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>37.16</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3663,15 +3677,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3679,25 +3693,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>8318.75</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>42.25</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3705,15 +3719,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3721,25 +3735,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>8459.9</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>40.94</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3747,15 +3761,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3763,22 +3777,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>9577.950000000001</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>45.21</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3786,15 +3800,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3802,22 +3816,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>10128.4</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>47.06</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3825,15 +3839,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3841,22 +3855,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>11131.6</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>50.49</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3864,15 +3878,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3880,22 +3894,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>12826.85</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>52.38</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3903,15 +3917,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3919,22 +3933,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>11362.6</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>46.77</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3942,15 +3956,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3958,22 +3972,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>10720.4</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>40.8</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3981,15 +3995,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3997,22 +4011,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>11842.85</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>41.51</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4020,15 +4034,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4036,22 +4050,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>12063.25</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>41.01</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4059,15 +4073,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4075,19 +4089,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>12289.45</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>40.78</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4095,15 +4109,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4111,19 +4125,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>10334.35</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>34.47</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4131,15 +4145,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4147,19 +4161,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>11514.9</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>38.39</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4167,15 +4181,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4183,10 +4197,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4263,30 +4277,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>11460.7</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>37.32</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.08333333333329999</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.0488048334537</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4296,30 +4310,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>11509.3</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>37.48</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.09848484848480001</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.0486741170237</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4329,30 +4343,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>11487.2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>37.41</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.08333333333329999</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.048762530474</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4472,4 +4486,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty India Consumption Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4385,6 +4388,712 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY India Consumption Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adani Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Asian Paints Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Britannia Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dixon Technologies (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DLF Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Eternal Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Havells India Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Indian Hotels Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Info Edge (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>InterGlobe Aviation Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Max Healthcare Institute Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tata Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tata Power Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Titan Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trent Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>United Spirits Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Varun Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4486,43 +5195,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty India Consumption Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11487.2</v>
+        <v>11546.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.41</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.09848484848484848</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>307.0622828120824</v>
+        <v>307.0757978723404</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04876253047402446</v>
+        <v>0.04875817107487102</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02673082063619353</v>
+        <v>0.02659574468085106</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.66666666666666</v>
+        <v>90.15151515151516</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.50501218960979</v>
+        <v>39.50326842994841</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.0181703235496</v>
+        <v>74.95704113504513</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>38.38004967681391</v>
+        <v>38.38004481919771</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11785.0656682036</v>
+        <v>11785.58288523132</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02593022391911037</v>
+        <v>0.02074587285100304</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>42.22104321309217</v>
+        <v>42.22094120315198</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12964.48991171966</v>
+        <v>12965.02920687907</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1286031332021433</v>
+        <v>0.1228973724242548</v>
       </c>
     </row>
     <row r="16">
@@ -4218,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4375,6 +4375,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>11546.05</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.0487581710749</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11546.05</v>
+        <v>11353.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.6</v>
+        <v>36.97</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.05303030303030303</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>307.0757978723404</v>
+        <v>307.0989991885313</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04875817107487102</v>
+        <v>0.04882226743746143</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02659574468085106</v>
+        <v>0.02704895861509332</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.15151515151516</v>
+        <v>94.6969696969697</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.50326842994841</v>
+        <v>39.52890697498457</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.95704113504513</v>
+        <v>78.14655088037415</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>38.38004481919771</v>
+        <v>38.38011624085889</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11785.58288523132</v>
+        <v>11786.49528630726</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02074587285100304</v>
+        <v>0.03814217584146307</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>42.22094120315198</v>
+        <v>42.22244105803659</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12965.02920687907</v>
+        <v>12966.46939221979</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1228973724242548</v>
+        <v>0.1420730608070488</v>
       </c>
     </row>
     <row r="16">
@@ -4218,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4408,6 +4408,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>11353.45</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.0488222674375</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4448,7 +4481,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11353.45</v>
+        <v>11415.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.97</v>
+        <v>37.17</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05303030303030303</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>307.0989991885313</v>
+        <v>307.1132633844498</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04882226743746143</v>
+        <v>0.04876998375469421</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02704895861509332</v>
+        <v>0.02690341673392521</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.6969696969697</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.52890697498457</v>
+        <v>39.50799350187769</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.14655088037415</v>
+        <v>76.01906471722997</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>38.38011624085889</v>
+        <v>38.38005798189809</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11786.49528630726</v>
+        <v>11787.02485570512</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03814217584146307</v>
+        <v>0.03255469415921675</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>42.22244105803659</v>
+        <v>42.22121761985984</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12966.46939221979</v>
+        <v>12966.69592730019</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1420730608070488</v>
+        <v>0.1358950126408351</v>
       </c>
     </row>
     <row r="16">
@@ -4218,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4441,6 +4441,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>11415.4</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.08333333333329999</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0487699837547</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4481,7 +4514,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11415.4</v>
+        <v>11270.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.17</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.05303030303030303</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>307.1132633844498</v>
+        <v>307.0871934604904</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04876998375469421</v>
+        <v>0.04886260536333031</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02690341673392521</v>
+        <v>0.02724795640326975</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.66666666666666</v>
+        <v>94.6969696969697</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.50799350187769</v>
+        <v>39.54504214533213</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.01906471722997</v>
+        <v>78.15139143147842</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>38.38005798189809</v>
+        <v>38.38016118883343</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11787.02485570512</v>
+        <v>11786.0559840401</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03255469415921675</v>
+        <v>0.04578095882379896</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>42.22121761985984</v>
+        <v>42.22338496550192</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12966.69592730019</v>
+        <v>12966.26078745785</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1358950126408351</v>
+        <v>0.1505009527384717</v>
       </c>
     </row>
     <row r="16">
@@ -4218,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4474,6 +4474,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>11270.1</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.0488626053633</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4514,7 +4547,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11270.1</v>
+        <v>11155.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.7</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>307.0871934604904</v>
+        <v>307.0671621249656</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04886260536333031</v>
+        <v>0.04863397191750551</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02724795640326975</v>
+        <v>0.02752546105147261</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.54504214533213</v>
+        <v>39.4535887670022</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.15139143147842</v>
+        <v>78.12395541797945</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>38.38016118883343</v>
+        <v>38.37840923946589</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11786.0559840401</v>
+        <v>11784.74921203335</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04578095882379896</v>
+        <v>0.05638340873839498</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>42.22338496550192</v>
+        <v>42.21803494286963</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12966.26078745785</v>
+        <v>12963.77218039961</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1505009527384717</v>
+        <v>0.1620708764896677</v>
       </c>
     </row>
     <row r="16">
@@ -4218,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4507,6 +4507,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>11155.75</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.0486339719175</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4547,7 +4580,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4617,17 +4650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adani Power Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4637,17 +4670,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4657,17 +4690,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4710,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4697,17 +4730,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -4717,17 +4750,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4737,17 +4770,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4757,17 +4790,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4810,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4797,17 +4830,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4817,17 +4850,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4857,17 +4890,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4877,17 +4910,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4897,17 +4930,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4917,12 +4950,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Info Edge (India) Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4937,17 +4970,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4957,17 +4990,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4977,17 +5010,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4997,12 +5030,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5017,17 +5050,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5070,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5090,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5077,17 +5110,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5097,17 +5130,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Power Co. Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5117,17 +5150,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,9 +568,9 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11155.75</v>
+        <v>11072.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.33</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05303030303030303</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>307.0671621249656</v>
+        <v>298.3737537052007</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04863397191750551</v>
+        <v>0.01434585534166</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02752546105147261</v>
+        <v>0.02694691457828079</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.6969696969697</v>
+        <v>92.53731343283582</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.4535887670022</v>
+        <v>25.738342136664</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.12395541797945</v>
+        <v>72.49762204398428</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>38.37840923946589</v>
+        <v>37.49446300129097</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11784.74921203335</v>
+        <v>11187.36366885595</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05638340873839498</v>
+        <v>0.01036009165429719</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>42.21803494286963</v>
+        <v>41.21395929226225</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12963.77218039961</v>
+        <v>12297.16373908562</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1620708764896677</v>
+        <v>0.1105890404813323</v>
       </c>
     </row>
     <row r="16">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
         <v>0.07458686346488497</v>
@@ -848,7 +848,9 @@
       <c r="E19" s="30" t="n">
         <v>0.1259240259405331</v>
       </c>
-      <c r="F19" s="30" t="n"/>
+      <c r="F19" s="30" t="n">
+        <v>0.1105827923566227</v>
+      </c>
       <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
@@ -860,10 +862,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.0007631659542847724</v>
+        <v>-0.0170781148475157</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.1206514405748893</v>
@@ -883,13 +885,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.08662685146493276</v>
+        <v>0.09168346372405001</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>0.07954667332385323</v>
+        <v>0.09700703254884635</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0.1148341626541892</v>
@@ -915,7 +917,7 @@
         <v>0.1933551716890769</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.121745661908498</v>
+        <v>0.116375497791126</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -936,7 +938,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -946,7 +948,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -969,7 +971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>11072.65</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2404,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2449,7 +2470,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2494,7 +2515,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2539,7 +2560,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2558,7 +2579,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2584,7 +2608,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2629,7 +2653,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2674,7 +2698,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2719,7 +2743,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2764,7 +2788,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2809,7 +2833,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2854,7 +2878,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2899,7 +2923,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2944,7 +2968,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2989,7 +3013,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3034,7 +3058,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3079,7 +3103,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3124,7 +3148,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3169,7 +3193,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3214,7 +3238,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3257,7 +3281,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3302,7 +3326,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3347,7 +3371,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3392,7 +3416,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3437,7 +3461,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3452,7 +3476,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3479,7 +3506,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3521,7 +3548,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3563,7 +3590,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3605,7 +3632,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3647,7 +3674,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3689,7 +3716,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3731,7 +3758,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3773,7 +3800,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3784,7 +3811,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3812,7 +3842,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3851,7 +3881,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3890,7 +3920,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3929,7 +3959,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3968,7 +3998,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4007,7 +4037,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4046,7 +4076,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4085,14 +4115,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4121,7 +4154,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4157,7 +4190,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4193,7 +4226,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4204,6 +4237,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>11072.65</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4218,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4226,7 +4295,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4540,6 +4609,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>11072.65</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.0746268656716</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.0143458553417</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4580,7 +4682,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11072.65</v>
+        <v>10862.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.11</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.07462686567164178</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.3737537052007</v>
+        <v>298.350727822027</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01434585534166</v>
+        <v>0.01419278387217005</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02694691457828079</v>
+        <v>0.02746498214776161</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>92.53731343283582</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.738342136664</v>
+        <v>25.67711354886802</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.49762204398428</v>
+        <v>74.04641764674996</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49446300129097</v>
+        <v>37.49047964430778</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11187.36366885595</v>
+        <v>11185.31188827611</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01036009165429719</v>
+        <v>0.02967535414193323</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21395929226225</v>
+        <v>41.21292015565793</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12297.16373908562</v>
+        <v>12295.90472411163</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1105890404813323</v>
+        <v>0.1319121163322696</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4642,6 +4642,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>10862.95</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0141927838722</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4682,7 +4715,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10862.95</v>
+        <v>10943.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.41</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.350727822027</v>
+        <v>298.3533260632498</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01419278387217005</v>
+        <v>0.01416545618337861</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02746498214776161</v>
+        <v>0.02726281352235551</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.67711354886802</v>
+        <v>25.66618247335144</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.04641764674996</v>
+        <v>74.04313832409498</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49047964430778</v>
+        <v>37.48976849976632</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11185.31188827611</v>
+        <v>11185.19712524653</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02967535414193323</v>
+        <v>0.02207656760540688</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21292015565793</v>
+        <v>41.21273463969059</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12295.90472411163</v>
+        <v>12295.9564559138</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1319121163322696</v>
+        <v>0.1235750992282061</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4675,6 +4675,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>10943.6</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.0141654561834</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4715,7 +4748,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10943.6</v>
+        <v>11074.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.68</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.3533260632498</v>
+        <v>298.4195634599839</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01416545618337861</v>
+        <v>0.01450382703323672</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02726281352235551</v>
+        <v>0.02694691457828079</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>92.53731343283582</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.66618247335144</v>
+        <v>25.80153081329469</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.04313832409498</v>
+        <v>72.51657864697349</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.48976849976632</v>
+        <v>37.49857387605348</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11185.19712524653</v>
+        <v>11190.30804646384</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02207656760540688</v>
+        <v>0.01047086704536482</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21273463969059</v>
+        <v>41.2150316943742</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12295.9564559138</v>
+        <v>12299.37176622455</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1235750992282061</v>
+        <v>0.110617938409437</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4708,6 +4708,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>11074.35</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0746268656716</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.0145038270332</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4748,7 +4781,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11074.35</v>
+        <v>10976.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.11</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.07462686567164178</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.4195634599839</v>
+        <v>298.3596085892906</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01450382703323672</v>
+        <v>0.01422597379096158</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02694691457828079</v>
+        <v>0.02718129926610492</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>92.53731343283582</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.80153081329469</v>
+        <v>25.69038951638463</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.51657864697349</v>
+        <v>74.05040043700494</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49857387605348</v>
+        <v>37.49134334082308</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11190.30804646384</v>
+        <v>11185.90252465468</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01047086704536482</v>
+        <v>0.01906342323520205</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.2150316943742</v>
+        <v>41.21314546779236</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12299.37176622455</v>
+        <v>12296.33795050402</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.110617938409437</v>
+        <v>0.1202268406575797</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4741,6 +4741,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>10976.65</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.014225973791</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4781,7 +4814,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10976.65</v>
+        <v>10741.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.3596085892906</v>
+        <v>298.3666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01422597379096158</v>
+        <v>0.01432201917565745</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02718129926610492</v>
+        <v>0.02777777777777778</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.69038951638463</v>
+        <v>25.72880767026298</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.05040043700494</v>
+        <v>75.10670200257144</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49134334082308</v>
+        <v>37.49384271614825</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11185.90252465468</v>
+        <v>11186.91287174143</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01906342323520205</v>
+        <v>0.04149563100411813</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21314546779236</v>
+        <v>41.21379747874675</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12296.33795050402</v>
+        <v>12296.82337440874</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1202268406575797</v>
+        <v>0.1448277077429652</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4774,6 +4774,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>10741.2</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.0143220191757</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4814,7 +4847,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10741.2</v>
+        <v>10903.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.3666666666667</v>
+        <v>298.3976464148878</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01432201917565745</v>
+        <v>0.01447073277477218</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.02736726874657909</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.72880767026298</v>
+        <v>25.78829310990887</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.10670200257144</v>
+        <v>74.07977151506222</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49384271614825</v>
+        <v>37.49771266889321</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11186.91287174143</v>
+        <v>11189.22920633946</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04149563100411813</v>
+        <v>0.02620997999160424</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21379747874675</v>
+        <v>41.21480703163674</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12296.82337440874</v>
+        <v>12298.40141568417</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1448277077429652</v>
+        <v>0.1279367003732004</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4807,6 +4807,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>10903.45</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.0144707327748</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4847,7 +4880,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10903.45</v>
+        <v>10823.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.54</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.3976464148878</v>
+        <v>298.4077750206782</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01447073277477218</v>
+        <v>0.01435543602345279</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02736726874657909</v>
+        <v>0.02757099531293079</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.78829310990887</v>
+        <v>25.74217440938112</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.07977151506222</v>
+        <v>74.0659359049039</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49771266889321</v>
+        <v>37.49471231800459</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11189.22920633946</v>
+        <v>11188.71367785617</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02620997999160424</v>
+        <v>0.03376653757939319</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21480703163674</v>
+        <v>41.21402433140493</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12298.40141568417</v>
+        <v>12298.58530038264</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1279367003732004</v>
+        <v>0.1363116716681809</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4840,6 +4840,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>10823.25</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.0143554360235</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4880,7 +4913,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10823.25</v>
+        <v>10948.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.27</v>
+        <v>36.69</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.4077750206782</v>
+        <v>298.4082856364132</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01435543602345279</v>
+        <v>0.01433294562771392</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02757099531293079</v>
+        <v>0.02725538293813028</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.74217440938112</v>
+        <v>25.73317825108557</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.0659359049039</v>
+        <v>74.06323705741522</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49471231800459</v>
+        <v>37.49412705364919</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11188.71367785617</v>
+        <v>11188.55817551332</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03376653757939319</v>
+        <v>0.02191679077811926</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21402433140493</v>
+        <v>41.21387165374699</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12298.58530038264</v>
+        <v>12298.56078463381</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1363116716681809</v>
+        <v>0.123299854285827</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4873,6 +4873,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>10948.6</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.0143329456277</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4913,7 +4946,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10948.6</v>
+        <v>10910</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.69</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.4082856364132</v>
+        <v>298.4135667396061</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01433294562771392</v>
+        <v>0.01444189323793488</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02725538293813028</v>
+        <v>0.02735229759299781</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.73317825108557</v>
+        <v>25.77675729517395</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.06323705741522</v>
+        <v>74.07631077064174</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49412705364919</v>
+        <v>37.49696218174603</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11188.55817551332</v>
+        <v>11189.60222655495</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02191679077811926</v>
+        <v>0.02562806842850174</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21387165374699</v>
+        <v>41.21461125238095</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12298.56078463381</v>
+        <v>12298.9991456093</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.123299854285827</v>
+        <v>0.1273143121548399</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4906,6 +4906,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>10910</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.0144418932379</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4946,7 +4979,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10910</v>
+        <v>11005.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.56</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.4135667396061</v>
+        <v>298.4069956616052</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01444189323793488</v>
+        <v>0.01440376361918227</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02735229759299781</v>
+        <v>0.02711496746203904</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.77675729517395</v>
+        <v>25.76150544767291</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.07631077064174</v>
+        <v>74.07173521639143</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49696218174603</v>
+        <v>37.49596994012432</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11189.60222655495</v>
+        <v>11189.05973925036</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02562806842850174</v>
+        <v>0.01670200488406515</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21461125238095</v>
+        <v>41.21435240674051</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12298.9991456093</v>
+        <v>12298.65107983408</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1273143121548399</v>
+        <v>0.1175258244777797</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4939,6 +4939,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>11005.25</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.0144037636192</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +5012,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11005.25</v>
+        <v>11054.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.88</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.4069956616052</v>
+        <v>298.7743243243243</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01440376361918227</v>
+        <v>0.01551222877521496</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02711496746203904</v>
+        <v>0.02702702702702703</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.76150544767291</v>
+        <v>26.20489151008599</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.07173521639143</v>
+        <v>74.20475103511535</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49596994012432</v>
+        <v>37.52481537052759</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11189.05973925036</v>
+        <v>11211.4513577244</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01670200488406515</v>
+        <v>0.01418419920344838</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21435240674051</v>
+        <v>41.22187730162832</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12298.65107983408</v>
+        <v>12316.0385381742</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1175258244777797</v>
+        <v>0.1141047919359004</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4972,6 +4972,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>11054.65</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.0155122287752</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5012,7 +5045,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11054.65</v>
+        <v>10938.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.7743243243243</v>
+        <v>298.7872166074843</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01551222877521496</v>
+        <v>0.01727994244608899</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.02731494127287626</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.20489151008599</v>
+        <v>26.9119769784356</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.20475103511535</v>
+        <v>74.41687667562023</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.52481537052759</v>
+        <v>37.57081633085422</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11211.4513577244</v>
+        <v>11225.67963716695</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01418419920344838</v>
+        <v>0.02624464165130358</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.22187730162832</v>
+        <v>41.23387755214831</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12316.0385381742</v>
+        <v>12320.15550374022</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1141047919359004</v>
+        <v>0.1263009437899021</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5005,6 +5005,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>10938.6</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.0172799424461</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5045,7 +5078,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10938.6</v>
+        <v>10833.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.61</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.7872166074843</v>
+        <v>298.7672366243794</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01727994244608899</v>
+        <v>0.01426533206845337</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02731494127287626</v>
+        <v>0.02757859900717044</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.9119769784356</v>
+        <v>25.70613282738135</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.41687667562023</v>
+        <v>74.05512343030396</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.57081633085422</v>
+        <v>37.49236755565563</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11225.67963716695</v>
+        <v>11201.49104910877</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02624464165130358</v>
+        <v>0.03398697064687339</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.23387755214831</v>
+        <v>41.21341265427041</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12320.15550374022</v>
+        <v>12313.2174105766</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1263009437899021</v>
+        <v>0.1366081813091675</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5038,6 +5038,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>10833.3</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.0142653320685</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5078,7 +5111,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10833.3</v>
+        <v>10753.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.26</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.7672366243794</v>
+        <v>298.8674263479711</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01426533206845337</v>
+        <v>0.01460545960190296</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02757859900717044</v>
+        <v>0.02779321845469706</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.70613282738135</v>
+        <v>25.84218384076118</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.05512343030396</v>
+        <v>75.14071485372089</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.49236755565563</v>
+        <v>37.50121864586895</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11201.49104910877</v>
+        <v>11207.8927016034</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03398697064687339</v>
+        <v>0.04227956214199402</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21341265427041</v>
+        <v>41.21572163432607</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12313.2174105766</v>
+        <v>12318.03664992543</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1366081813091675</v>
+        <v>0.1455175551508079</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5071,6 +5071,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>10753.25</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.0146054596019</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5111,7 +5144,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10753.25</v>
+        <v>10726.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.98</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>298.8674263479711</v>
+        <v>299.2119944211994</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01460545960190296</v>
+        <v>0.01569842541305211</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02779321845469706</v>
+        <v>0.02789400278940028</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.84218384076118</v>
+        <v>26.27937016522084</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.14071485372089</v>
+        <v>75.27187075105878</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.50121864586895</v>
+        <v>37.5296607390345</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11207.8927016034</v>
+        <v>11229.3246396775</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04227956214199402</v>
+        <v>0.04685246133987464</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21572163432607</v>
+        <v>41.22314131080404</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12318.03664992543</v>
+        <v>12334.45832791261</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1455175551508079</v>
+        <v>0.1498784187114097</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5104,6 +5104,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>10726.75</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.0156984254131</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5144,7 +5177,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10726.75</v>
+        <v>10804.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.85</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>299.2119944211994</v>
+        <v>299.2093602880089</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01569842541305211</v>
+        <v>0.01518848465762401</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02789400278940028</v>
+        <v>0.02769315978953199</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.27937016522084</v>
+        <v>26.07539386304961</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.27187075105878</v>
+        <v>75.21067786040742</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.5296607390345</v>
+        <v>37.51639062360468</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11229.3246396775</v>
+        <v>11225.25523880381</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04685246133987464</v>
+        <v>0.03894740026598398</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.22314131080404</v>
+        <v>41.21967954156148</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12334.45832791261</v>
+        <v>12333.31394690734</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1498784187114097</v>
+        <v>0.1415031720177646</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5137,6 +5137,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>10804.45</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.0151884846576</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5177,7 +5210,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10804.45</v>
+        <v>10936.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.11</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>299.2093602880089</v>
+        <v>299.0607054963085</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01518848465762401</v>
+        <v>0.0147747133924645</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02769315978953199</v>
+        <v>0.02734481815695925</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.07539386304961</v>
+        <v>25.9098853569858</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.21067786040742</v>
+        <v>74.1162491891853</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.51639062360468</v>
+        <v>37.50562311308162</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11225.25523880381</v>
+        <v>11216.45810827684</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03894740026598398</v>
+        <v>0.02558444389066517</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21967954156148</v>
+        <v>41.21687062577285</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12333.31394690734</v>
+        <v>12326.3464076937</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1415031720177646</v>
+        <v>0.1270678322606742</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5170,6 +5170,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>10936.65</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.0147747133925</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5210,7 +5243,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10936.65</v>
+        <v>10944.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.57</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>299.0607054963085</v>
+        <v>299.6809967141292</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0147747133924645</v>
+        <v>0.01699696815601182</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02734481815695925</v>
+        <v>0.02738225629791895</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.9098853569858</v>
+        <v>26.79878726240473</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.1162491891853</v>
+        <v>74.38291976081098</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.50562311308162</v>
+        <v>37.56345253132844</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11216.45810827684</v>
+        <v>11257.05289461239</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02558444389066517</v>
+        <v>0.02857208464754768</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.21687062577285</v>
+        <v>41.23195656096767</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12326.3464076937</v>
+        <v>12356.43383866447</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1270678322606742</v>
+        <v>0.1290240022170774</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5203,6 +5203,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>10944.35</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.016996968156</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5243,7 +5276,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10944.35</v>
+        <v>11059.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.52</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>299.6809967141292</v>
+        <v>299.7059620596206</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01699696815601182</v>
+        <v>0.01541521900676113</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02738225629791895</v>
+        <v>0.02710027100271003</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.79878726240473</v>
+        <v>26.16608760270445</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.38291976081098</v>
+        <v>74.19310986290088</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.56345253132844</v>
+        <v>37.52229089918166</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11257.05289461239</v>
+        <v>11245.65429262019</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02857208464754768</v>
+        <v>0.01686425201034303</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.23195656096767</v>
+        <v>41.2212187438859</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12356.43383866447</v>
+        <v>12354.24502090639</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1290240022170774</v>
+        <v>0.1171061990212983</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5236,6 +5236,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>11059.15</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.0154152190068</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5276,7 +5309,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-india-consumption.xlsx
+++ b/docs/downloads/indices/nifty-india-consumption.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>11059.15</v>
+        <v>11090.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.9</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>299.7059620596206</v>
+        <v>302.4461412598855</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01541521900676113</v>
+        <v>0.02484749570184364</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02710027100271003</v>
+        <v>0.02727024815925825</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.16608760270445</v>
+        <v>29.93899828073745</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.19310986290088</v>
+        <v>75.32498306631079</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>37.52229089918166</v>
+        <v>37.79585325897135</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>11245.65429262019</v>
+        <v>11431.20997380075</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01686425201034303</v>
+        <v>0.03070229776305822</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.2212187438859</v>
+        <v>41.44362692584032</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>12354.24502090639</v>
+        <v>12534.46504353469</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1171061990212983</v>
+        <v>0.1301779908873826</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5269,6 +5269,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>11090.7</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.0248474957018</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5309,7 +5342,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
